--- a/EXCEL/class notes/day14 chart&subtotal&text fn/subTotal.xlsx
+++ b/EXCEL/class notes/day14 chart&subtotal&text fn/subTotal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day14 chart&amp;subtotal&amp;text fn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B2A6D5-0CD1-4576-B9E9-D136A1EA70EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A7A520-80A6-4E97-8AA0-F3E538D19908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{BBE4EA2F-3B01-46ED-AB24-202C24F0676C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{BBE4EA2F-3B01-46ED-AB24-202C24F0676C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId1"/>
@@ -31,6 +31,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1266,6 +1275,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1273,7 +1283,411 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Total %'!$B$1:$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Name</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Nme1 </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Nme2 </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Nme3 </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Nme4 </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Nme5 </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> Nme6 </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Nme7 </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Nme8 </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Nme9 </c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v> Nme10 </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Total %'!$C$1:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000016-301C-4D7B-B38B-15B26C0CC261}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1309,6 +1723,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1867,20 +2321,539 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>479425</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>212725</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>151130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>174625</xdr:colOff>
+      <xdr:colOff>517525</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1900,6 +2873,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EF0A4B9-0361-FF4B-C9B9-D02937936EBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2206,13 +3215,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8245E947-279D-4908-A546-FB7AFB4733E8}">
   <dimension ref="A2:K60"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="2" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F2" t="s">
         <v>27</v>
       </c>
@@ -2229,7 +3238,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G3" t="s">
         <v>28</v>
       </c>
@@ -2240,7 +3249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -2254,7 +3263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -2268,7 +3277,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2288,7 +3297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>15</v>
       </c>
@@ -2302,7 +3311,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>15</v>
       </c>
@@ -2316,7 +3325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>15</v>
       </c>
@@ -2330,7 +3339,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>15</v>
       </c>
@@ -2344,7 +3353,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
@@ -2358,7 +3367,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>15</v>
       </c>
@@ -2372,7 +3381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>15</v>
       </c>
@@ -2386,7 +3395,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>15</v>
       </c>
@@ -2400,7 +3409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>22</v>
       </c>
@@ -2411,7 +3420,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="16" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
         <v>5</v>
       </c>
@@ -2425,7 +3434,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>5</v>
       </c>
@@ -2439,7 +3448,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
         <v>5</v>
       </c>
@@ -2453,7 +3462,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>5</v>
       </c>
@@ -2467,7 +3476,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
         <v>5</v>
       </c>
@@ -2481,7 +3490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>5</v>
       </c>
@@ -2495,7 +3504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
         <v>5</v>
       </c>
@@ -2509,7 +3518,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
         <v>5</v>
       </c>
@@ -2523,7 +3532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A24" s="34" t="s">
         <v>5</v>
       </c>
@@ -2537,7 +3546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>5</v>
       </c>
@@ -2551,7 +3560,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>21</v>
       </c>
@@ -2562,7 +3571,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="27" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>18</v>
       </c>
@@ -2576,7 +3585,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>18</v>
       </c>
@@ -2590,7 +3599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>18</v>
       </c>
@@ -2604,7 +3613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>18</v>
       </c>
@@ -2618,7 +3627,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>18</v>
       </c>
@@ -2632,7 +3641,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>18</v>
       </c>
@@ -2646,7 +3655,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>18</v>
       </c>
@@ -2660,7 +3669,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>18</v>
       </c>
@@ -2674,7 +3683,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>18</v>
       </c>
@@ -2688,7 +3697,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>18</v>
       </c>
@@ -2702,7 +3711,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>25</v>
       </c>
@@ -2713,7 +3722,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="38" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>17</v>
       </c>
@@ -2727,7 +3736,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
         <v>17</v>
       </c>
@@ -2741,7 +3750,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A40" s="35" t="s">
         <v>17</v>
       </c>
@@ -2755,7 +3764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A41" s="35" t="s">
         <v>17</v>
       </c>
@@ -2769,7 +3778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
         <v>17</v>
       </c>
@@ -2783,7 +3792,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A43" s="35" t="s">
         <v>17</v>
       </c>
@@ -2797,7 +3806,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
         <v>17</v>
       </c>
@@ -2811,7 +3820,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
         <v>17</v>
       </c>
@@ -2825,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
         <v>17</v>
       </c>
@@ -2839,7 +3848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>17</v>
       </c>
@@ -2853,7 +3862,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A48" s="36" t="s">
         <v>24</v>
       </c>
@@ -2864,7 +3873,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="49" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>16</v>
       </c>
@@ -2878,7 +3887,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>16</v>
       </c>
@@ -2892,7 +3901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>16</v>
       </c>
@@ -2906,7 +3915,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>16</v>
       </c>
@@ -2920,7 +3929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>16</v>
       </c>
@@ -2934,7 +3943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>16</v>
       </c>
@@ -2948,7 +3957,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>16</v>
       </c>
@@ -2962,7 +3971,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>16</v>
       </c>
@@ -2976,7 +3985,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>16</v>
       </c>
@@ -2990,7 +3999,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>16</v>
       </c>
@@ -3004,7 +4013,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="59" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>23</v>
       </c>
@@ -3014,7 +4023,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>26</v>
       </c>
@@ -3048,13 +4057,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60910427-5AEC-4BFA-B0EB-489538763583}">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="3" width="8.7265625" customWidth="1"/>
+    <col min="2" max="3" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>28</v>
       </c>
@@ -3095,7 +4104,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C2">
         <f>SUM(D:D)</f>
         <v>2378</v>
@@ -3149,7 +4158,7 @@
         <v>999.80640000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E3">
         <f>SUBTOTAL(P$1,$D:$D)</f>
         <v>2378</v>
@@ -3170,7 +4179,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -3231,7 +4240,7 @@
         <v>999.80640000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -3278,7 +4287,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -3292,7 +4301,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="39" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
         <v>15</v>
       </c>
@@ -3306,7 +4315,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>15</v>
       </c>
@@ -3320,7 +4329,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>15</v>
       </c>
@@ -3334,7 +4343,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>15</v>
       </c>
@@ -3348,7 +4357,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>15</v>
       </c>
@@ -3362,7 +4371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>15</v>
       </c>
@@ -3376,7 +4385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>15</v>
       </c>
@@ -3390,7 +4399,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>15</v>
       </c>
@@ -3404,7 +4413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>5</v>
       </c>
@@ -3418,7 +4427,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>5</v>
       </c>
@@ -3432,7 +4441,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>5</v>
       </c>
@@ -3446,7 +4455,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>5</v>
       </c>
@@ -3460,7 +4469,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>5</v>
       </c>
@@ -3474,7 +4483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>5</v>
       </c>
@@ -3488,7 +4497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>5</v>
       </c>
@@ -3502,7 +4511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>5</v>
       </c>
@@ -3516,7 +4525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>5</v>
       </c>
@@ -3530,7 +4539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>5</v>
       </c>
@@ -3544,7 +4553,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>18</v>
       </c>
@@ -3558,7 +4567,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>18</v>
       </c>
@@ -3572,7 +4581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>18</v>
       </c>
@@ -3586,7 +4595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>18</v>
       </c>
@@ -3600,7 +4609,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>18</v>
       </c>
@@ -3614,7 +4623,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>18</v>
       </c>
@@ -3628,7 +4637,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>18</v>
       </c>
@@ -3642,7 +4651,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>18</v>
       </c>
@@ -3656,7 +4665,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>18</v>
       </c>
@@ -3670,7 +4679,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>18</v>
       </c>
@@ -3684,7 +4693,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>17</v>
       </c>
@@ -3698,7 +4707,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>17</v>
       </c>
@@ -3712,7 +4721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>17</v>
       </c>
@@ -3726,7 +4735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>17</v>
       </c>
@@ -3740,7 +4749,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>17</v>
       </c>
@@ -3754,7 +4763,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>17</v>
       </c>
@@ -3768,7 +4777,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>17</v>
       </c>
@@ -3782,7 +4791,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>17</v>
       </c>
@@ -3796,7 +4805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>17</v>
       </c>
@@ -3810,7 +4819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>17</v>
       </c>
@@ -3824,7 +4833,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>16</v>
       </c>
@@ -3838,7 +4847,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>16</v>
       </c>
@@ -3852,7 +4861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>16</v>
       </c>
@@ -3866,7 +4875,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>16</v>
       </c>
@@ -3880,7 +4889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>16</v>
       </c>
@@ -3894,7 +4903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>16</v>
       </c>
@@ -3908,7 +4917,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>16</v>
       </c>
@@ -3922,7 +4931,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>16</v>
       </c>
@@ -3936,7 +4945,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>16</v>
       </c>
@@ -3950,7 +4959,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>16</v>
       </c>
@@ -3983,14 +4992,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437EB11C-FB9D-4A64-B35D-2341D1B9231C}">
   <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>3</v>
       </c>
@@ -4010,7 +5019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>15</v>
       </c>
@@ -4024,7 +5033,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>15</v>
       </c>
@@ -4038,7 +5047,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>15</v>
       </c>
@@ -4055,7 +5064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>15</v>
       </c>
@@ -4072,7 +5081,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>15</v>
       </c>
@@ -4089,7 +5098,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
@@ -4106,7 +5115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
@@ -4120,7 +5129,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
@@ -4134,7 +5143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>15</v>
       </c>
@@ -4148,7 +5157,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>15</v>
       </c>
@@ -4162,7 +5171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>5</v>
       </c>
@@ -4176,7 +5185,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>5</v>
       </c>
@@ -4190,7 +5199,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>5</v>
       </c>
@@ -4204,7 +5213,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>5</v>
       </c>
@@ -4218,7 +5227,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>5</v>
       </c>
@@ -4232,7 +5241,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>5</v>
       </c>
@@ -4246,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>5</v>
       </c>
@@ -4260,7 +5269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>5</v>
       </c>
@@ -4274,7 +5283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>5</v>
       </c>
@@ -4288,7 +5297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>5</v>
       </c>
@@ -4302,7 +5311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>18</v>
       </c>
@@ -4316,7 +5325,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>18</v>
       </c>
@@ -4330,7 +5339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>18</v>
       </c>
@@ -4344,7 +5353,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>18</v>
       </c>
@@ -4358,7 +5367,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>18</v>
       </c>
@@ -4372,7 +5381,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>18</v>
       </c>
@@ -4386,7 +5395,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>18</v>
       </c>
@@ -4400,7 +5409,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>18</v>
       </c>
@@ -4414,7 +5423,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>18</v>
       </c>
@@ -4428,7 +5437,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>18</v>
       </c>
@@ -4442,7 +5451,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>17</v>
       </c>
@@ -4456,7 +5465,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>17</v>
       </c>
@@ -4470,7 +5479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>17</v>
       </c>
@@ -4484,7 +5493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>17</v>
       </c>
@@ -4498,7 +5507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>17</v>
       </c>
@@ -4512,7 +5521,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>17</v>
       </c>
@@ -4526,7 +5535,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="16" t="s">
         <v>17</v>
       </c>
@@ -4540,7 +5549,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>17</v>
       </c>
@@ -4554,7 +5563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>17</v>
       </c>
@@ -4568,7 +5577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>17</v>
       </c>
@@ -4582,7 +5591,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>16</v>
       </c>
@@ -4596,7 +5605,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>16</v>
       </c>
@@ -4610,7 +5619,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>16</v>
       </c>
@@ -4624,7 +5633,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>16</v>
       </c>
@@ -4638,7 +5647,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>16</v>
       </c>
@@ -4652,7 +5661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>16</v>
       </c>
@@ -4666,7 +5675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>16</v>
       </c>
@@ -4680,7 +5689,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>16</v>
       </c>
@@ -4694,7 +5703,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>16</v>
       </c>
@@ -4708,7 +5717,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="17" t="s">
         <v>16</v>
       </c>
@@ -4740,18 +5749,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9E29420-61BC-45D0-AD25-19E79A8F83AF}">
-  <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C2">
         <f>SUM(D6:D55)</f>
         <v>2279</v>
@@ -4760,7 +5769,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>35</v>
       </c>
@@ -4776,12 +5785,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G4" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -4798,7 +5807,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -4816,7 +5825,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -4834,7 +5843,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -4852,7 +5861,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -4870,7 +5879,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -4887,8 +5896,12 @@
         <f t="shared" si="0"/>
         <v>Fail</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H10">
+        <f>SUBTOTAL(9,D:D)</f>
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -4906,7 +5919,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -4924,7 +5937,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -4942,7 +5955,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -4960,7 +5973,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -4978,7 +5991,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
@@ -4996,7 +6009,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
@@ -5014,7 +6027,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
@@ -5032,7 +6045,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
@@ -5050,7 +6063,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>5</v>
       </c>
@@ -5068,7 +6081,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>5</v>
       </c>
@@ -5086,7 +6099,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
@@ -5104,7 +6117,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>5</v>
       </c>
@@ -5122,7 +6135,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>5</v>
       </c>
@@ -5140,7 +6153,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>5</v>
       </c>
@@ -5158,7 +6171,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>18</v>
       </c>
@@ -5176,7 +6189,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>18</v>
       </c>
@@ -5194,7 +6207,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
@@ -5212,7 +6225,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>18</v>
       </c>
@@ -5230,7 +6243,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>18</v>
       </c>
@@ -5248,7 +6261,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>18</v>
       </c>
@@ -5266,7 +6279,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>18</v>
       </c>
@@ -5284,7 +6297,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -5302,7 +6315,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>18</v>
       </c>
@@ -5320,7 +6333,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>18</v>
       </c>
@@ -5338,7 +6351,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>17</v>
       </c>
@@ -5356,7 +6369,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>17</v>
       </c>
@@ -5374,7 +6387,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -5392,7 +6405,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>17</v>
       </c>
@@ -5410,7 +6423,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>17</v>
       </c>
@@ -5428,7 +6441,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>17</v>
       </c>
@@ -5446,7 +6459,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>17</v>
       </c>
@@ -5464,7 +6477,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>17</v>
       </c>
@@ -5482,7 +6495,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>17</v>
       </c>
@@ -5500,7 +6513,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>17</v>
       </c>
@@ -5518,7 +6531,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>16</v>
       </c>
@@ -5536,7 +6549,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>16</v>
       </c>
@@ -5554,7 +6567,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>16</v>
       </c>
@@ -5572,7 +6585,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>16</v>
       </c>
@@ -5590,7 +6603,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>16</v>
       </c>
@@ -5608,7 +6621,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>16</v>
       </c>
@@ -5626,7 +6639,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>16</v>
       </c>
@@ -5644,7 +6657,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>16</v>
       </c>
@@ -5662,7 +6675,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5680,7 +6693,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>16</v>
       </c>
@@ -5718,12 +6731,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B53DFCE-9F3F-47B8-A37B-51A2F8495456}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
@@ -5737,7 +6750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="50">
         <v>1001</v>
       </c>
@@ -5752,7 +6765,7 @@
         <v>0.15010570824524314</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="52">
         <v>1002</v>
       </c>
@@ -5767,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="52">
         <v>1003</v>
       </c>
@@ -5782,7 +6795,7 @@
         <v>0.21141649048625794</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="52">
         <v>1004</v>
       </c>
@@ -5797,7 +6810,7 @@
         <v>3.1712473572938688E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>1005</v>
       </c>
@@ -5812,7 +6825,7 @@
         <v>9.7251585623678652E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="52">
         <v>1006</v>
       </c>
@@ -5827,7 +6840,7 @@
         <v>0.1839323467230444</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="52">
         <v>1007</v>
       </c>
@@ -5842,7 +6855,7 @@
         <v>4.8625792811839326E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="52">
         <v>1008</v>
       </c>
@@ -5857,7 +6870,7 @@
         <v>0.18816067653276955</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="52">
         <v>1009</v>
       </c>
@@ -5872,7 +6885,7 @@
         <v>7.1881606765327691E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="53">
         <v>1010</v>
       </c>
@@ -5887,10 +6900,10 @@
         <v>1.6913319238900635E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C12" s="31"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C13" s="32">
         <f>SUM(C2:C12)</f>
         <v>473</v>
@@ -5915,15 +6928,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C54B467-9378-4638-A02C-BDA7D6B9CEF1}">
   <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" customWidth="1"/>
-    <col min="2" max="3" width="8.7265625" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="2" max="3" width="8.77734375" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C1">
         <f>SUM(D4:D1048576)</f>
         <v>2378</v>
@@ -5933,7 +6946,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -5947,7 +6960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -5967,7 +6980,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -5984,7 +6997,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -6004,7 +7017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -6018,7 +7031,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -6032,7 +7045,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -6046,7 +7059,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -6060,7 +7073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
@@ -6074,7 +7087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -6088,7 +7101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
@@ -6102,7 +7115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
         <v>15</v>
       </c>
@@ -6116,7 +7129,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>15</v>
       </c>
@@ -6130,7 +7143,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="33" t="s">
         <v>15</v>
       </c>
@@ -6144,7 +7157,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="33" t="s">
         <v>15</v>
       </c>
@@ -6158,7 +7171,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="33" t="s">
         <v>15</v>
       </c>
@@ -6172,7 +7185,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="33" t="s">
         <v>15</v>
       </c>
@@ -6186,7 +7199,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="33" t="s">
         <v>15</v>
       </c>
@@ -6200,7 +7213,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="33" t="s">
         <v>15</v>
       </c>
@@ -6214,7 +7227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="33" t="s">
         <v>15</v>
       </c>
@@ -6228,7 +7241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="33" t="s">
         <v>15</v>
       </c>
@@ -6242,7 +7255,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
@@ -6256,7 +7269,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>16</v>
       </c>
@@ -6270,7 +7283,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
@@ -6284,7 +7297,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>16</v>
       </c>
@@ -6298,7 +7311,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>16</v>
       </c>
@@ -6312,7 +7325,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>16</v>
       </c>
@@ -6326,7 +7339,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>16</v>
       </c>
@@ -6340,7 +7353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>16</v>
       </c>
@@ -6354,7 +7367,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>16</v>
       </c>
@@ -6368,7 +7381,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>16</v>
       </c>
@@ -6382,7 +7395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="33" t="s">
         <v>17</v>
       </c>
@@ -6396,7 +7409,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="33" t="s">
         <v>17</v>
       </c>
@@ -6410,7 +7423,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>17</v>
       </c>
@@ -6424,7 +7437,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="33" t="s">
         <v>17</v>
       </c>
@@ -6438,7 +7451,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="33" t="s">
         <v>17</v>
       </c>
@@ -6452,7 +7465,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="33" t="s">
         <v>17</v>
       </c>
@@ -6466,7 +7479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>17</v>
       </c>
@@ -6480,7 +7493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="33" t="s">
         <v>17</v>
       </c>
@@ -6494,7 +7507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
         <v>17</v>
       </c>
@@ -6508,7 +7521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>17</v>
       </c>
@@ -6522,7 +7535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -6536,7 +7549,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>18</v>
       </c>
@@ -6550,7 +7563,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>18</v>
       </c>
@@ -6564,7 +7577,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>18</v>
       </c>
@@ -6578,7 +7591,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>18</v>
       </c>
@@ -6592,7 +7605,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>18</v>
       </c>
@@ -6606,7 +7619,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>18</v>
       </c>
@@ -6620,7 +7633,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>18</v>
       </c>
@@ -6634,7 +7647,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>18</v>
       </c>
@@ -6648,7 +7661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>18</v>
       </c>
